--- a/data/case-study-a-customer-satisfaction-survey--satisfaction_survey.xlsx
+++ b/data/case-study-a-customer-satisfaction-survey--satisfaction_survey.xlsx
@@ -24459,7 +24459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a customer satisfaction survey, one row per respondent.</t>
+          <t>WHAT IS CAPTURED: a customer satisfaction survey, one row per respondent (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
